--- a/alocacao/saidas_1250_40/resumo_custos.xlsx
+++ b/alocacao/saidas_1250_40/resumo_custos.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Resultados_Custos" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Resultados_Custos" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +45,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -429,77 +441,77 @@
     <col width="19" customWidth="1" min="7" max="7"/>
     <col width="27" customWidth="1" min="8" max="8"/>
     <col width="19" customWidth="1" min="9" max="9"/>
-    <col width="114" customWidth="1" min="10" max="10"/>
-    <col width="120" customWidth="1" min="11" max="11"/>
+    <col width="90" customWidth="1" min="10" max="10"/>
+    <col width="96" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Nome da Instância</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Total de Entregas</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Pico de Abastecimento (Max/Dia)</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Custo Modelo Exato (M1)</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Custo Modelo Anual (M2)</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Custo Heurística</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Gap Heurística vs M1 (%)</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Gap M2 vs M1 (%)</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Caminho da Entrada</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Pasta de Saída</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="inlineStr">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>abastecimento_00_1250</t>
         </is>
       </c>
-      <c r="B2" s="2" t="n">
+      <c r="B2" s="3" t="n">
         <v>17061</v>
       </c>
-      <c r="C2" s="2" t="n">
+      <c r="C2" s="3" t="n">
         <v>110</v>
       </c>
       <c r="D2" t="inlineStr">
@@ -507,158 +519,158 @@
           <t>Sucesso</t>
         </is>
       </c>
-      <c r="E2" s="3" t="n">
+      <c r="E2" s="4" t="n">
         <v>912978.58</v>
       </c>
-      <c r="F2" s="3" t="n">
+      <c r="F2" s="4" t="n">
         <v>916844.67</v>
       </c>
-      <c r="G2" s="3" t="n">
+      <c r="G2" s="4" t="n">
         <v>1259398.13</v>
       </c>
-      <c r="H2" s="4" t="n">
+      <c r="H2" s="5" t="n">
         <v>37.94</v>
       </c>
-      <c r="I2" s="4" t="n">
+      <c r="I2" s="5" t="n">
         <v>0.42</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>C:\Users\lfeli\Documents\AlocacaoCarros\ModelsAndHeristics\alocacao\entradas_1250\abastecimento_00_1250.csv</t>
+          <t>/home/guilherme/ModelsAndHeristics/alocacao/entradas_1250/abastecimento_00_1250.csv</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>C:\Users\lfeli\Documents\AlocacaoCarros\ModelsAndHeristics\alocacao\saidas_1250_40\alocacao_abastecimento_00_1250</t>
+          <t>/home/guilherme/ModelsAndHeristics/alocacao/saidas_1250_40/alocacao_abastecimento_00_1250</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="inlineStr">
-        <is>
-          <t>abastecimento_10wlim_1250</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="n">
-        <v>17602</v>
-      </c>
-      <c r="C3" s="2" t="n">
-        <v>77</v>
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>abastecimento_full_1250</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="n">
+        <v>17271</v>
+      </c>
+      <c r="C3" s="3" t="n">
+        <v>370</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
           <t>Sucesso</t>
         </is>
       </c>
-      <c r="E3" s="3" t="n">
-        <v>953429.11</v>
-      </c>
-      <c r="F3" s="3" t="n">
-        <v>990039.77</v>
-      </c>
-      <c r="G3" s="3" t="n">
-        <v>1350401.97</v>
-      </c>
-      <c r="H3" s="4" t="n">
-        <v>41.64</v>
-      </c>
-      <c r="I3" s="4" t="n">
-        <v>3.84</v>
+      <c r="E3" s="4" t="n">
+        <v>977683.91</v>
+      </c>
+      <c r="F3" s="4" t="n">
+        <v>1071061.64</v>
+      </c>
+      <c r="G3" s="4" t="n">
+        <v>1482780.51</v>
+      </c>
+      <c r="H3" s="5" t="n">
+        <v>51.66</v>
+      </c>
+      <c r="I3" s="5" t="n">
+        <v>9.550000000000001</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>C:\Users\lfeli\Documents\AlocacaoCarros\ModelsAndHeristics\alocacao\entradas_1250\abastecimento_10wlim_1250.csv</t>
+          <t>/home/guilherme/ModelsAndHeristics/alocacao/entradas_1250/abastecimento_full_1250.csv</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>C:\Users\lfeli\Documents\AlocacaoCarros\ModelsAndHeristics\alocacao\saidas_1250_40\alocacao_abastecimento_10wlim_1250</t>
+          <t>/home/guilherme/ModelsAndHeristics/alocacao/saidas_1250_40/alocacao_abastecimento_full_1250</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="inlineStr">
-        <is>
-          <t>abastecimento_full_1250</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="n">
-        <v>16879</v>
-      </c>
-      <c r="C4" s="2" t="n">
-        <v>402</v>
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>abastecimento_limite_1250</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="n">
+        <v>17106</v>
+      </c>
+      <c r="C4" s="3" t="n">
+        <v>301</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
           <t>Sucesso</t>
         </is>
       </c>
-      <c r="E4" s="3" t="n">
-        <v>952888.8</v>
-      </c>
-      <c r="F4" s="3" t="n">
-        <v>1040361.88</v>
-      </c>
-      <c r="G4" s="3" t="n">
-        <v>1410417.54</v>
-      </c>
-      <c r="H4" s="4" t="n">
-        <v>48.01</v>
-      </c>
-      <c r="I4" s="4" t="n">
-        <v>9.18</v>
+      <c r="E4" s="4" t="n">
+        <v>979350.45</v>
+      </c>
+      <c r="F4" s="4" t="n">
+        <v>1075945.57</v>
+      </c>
+      <c r="G4" s="4" t="n">
+        <v>1482252.61</v>
+      </c>
+      <c r="H4" s="5" t="n">
+        <v>51.35</v>
+      </c>
+      <c r="I4" s="5" t="n">
+        <v>9.859999999999999</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>C:\Users\lfeli\Documents\AlocacaoCarros\ModelsAndHeristics\alocacao\entradas_1250\abastecimento_full_1250.csv</t>
+          <t>/home/guilherme/ModelsAndHeristics/alocacao/entradas_1250/abastecimento_limite_1250.csv</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>C:\Users\lfeli\Documents\AlocacaoCarros\ModelsAndHeristics\alocacao\saidas_1250_40\alocacao_abastecimento_full_1250</t>
+          <t>/home/guilherme/ModelsAndHeristics/alocacao/saidas_1250_40/alocacao_abastecimento_limite_1250</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="inlineStr">
-        <is>
-          <t>abastecimento_limite_1250</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="n">
-        <v>16724</v>
-      </c>
-      <c r="C5" s="2" t="n">
-        <v>245</v>
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>abastecimento_10wlim_1250</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="n">
+        <v>17602</v>
+      </c>
+      <c r="C5" s="3" t="n">
+        <v>77</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
           <t>Sucesso</t>
         </is>
       </c>
-      <c r="E5" s="3" t="n">
-        <v>941018.42</v>
-      </c>
-      <c r="F5" s="3" t="n">
-        <v>1041580.94</v>
-      </c>
-      <c r="G5" s="3" t="n">
-        <v>1418584.23</v>
-      </c>
-      <c r="H5" s="4" t="n">
-        <v>50.75</v>
-      </c>
-      <c r="I5" s="4" t="n">
-        <v>10.69</v>
+      <c r="E5" s="4" t="n">
+        <v>953429.11</v>
+      </c>
+      <c r="F5" s="4" t="n">
+        <v>990056.72</v>
+      </c>
+      <c r="G5" s="4" t="n">
+        <v>1350401.97</v>
+      </c>
+      <c r="H5" s="5" t="n">
+        <v>41.64</v>
+      </c>
+      <c r="I5" s="5" t="n">
+        <v>3.84</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>C:\Users\lfeli\Documents\AlocacaoCarros\ModelsAndHeristics\alocacao\entradas_1250\abastecimento_limite_1250.csv</t>
+          <t>/home/guilherme/ModelsAndHeristics/alocacao/entradas_1250/abastecimento_10wlim_1250.csv</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>C:\Users\lfeli\Documents\AlocacaoCarros\ModelsAndHeristics\alocacao\saidas_1250_40\alocacao_abastecimento_limite_1250</t>
+          <t>/home/guilherme/ModelsAndHeristics/alocacao/saidas_1250_40/alocacao_abastecimento_10wlim_1250</t>
         </is>
       </c>
     </row>
